--- a/data_lake/macro/China/China CPI.xlsx
+++ b/data_lake/macro/China/China CPI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6405A3-3AB7-4865-BD4D-4F92108E2516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2706F69F-16D7-489B-9998-46F755F205FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
   </bookViews>
@@ -66,7 +66,7 @@
   </si>
   <si>
     <t>UTC+8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Time Zone</t>
@@ -77,35 +77,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -113,7 +107,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -121,7 +115,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -144,40 +144,40 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4280,14 +4280,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A2DF88-805C-2E4E-A3EC-9F545567B7EC}">
   <dimension ref="A1:I484"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.796875" style="8"/>
-    <col min="2" max="2" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.796875" style="9"/>
-    <col min="4" max="4" width="10.796875" style="13"/>
-    <col min="5" max="7" width="10.796875" style="11"/>
-    <col min="8" max="16384" width="10.796875" style="6"/>
+    <col min="1" max="1" width="8.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -15908,7 +15910,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G481">
     <sortCondition ref="B2:B481"/>
   </sortState>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -15917,9 +15919,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91024DA1-00F0-4602-9985-01AD43B6ED3C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -15928,9 +15930,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651FE52F-B836-C048-8E04-77D870B1C558}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -15938,7 +15940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -15947,7 +15949,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{576E4B7C-CE33-3440-8ED0-74DD24CFDFDE}"/>
   </hyperlinks>

--- a/data_lake/macro/China/China CPI.xlsx
+++ b/data_lake/macro/China/China CPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/China/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB4F94-D894-423C-B333-FB12C884E156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC38E359-B276-DD4C-BE67-E8577C8D1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20800" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
   </bookViews>
   <sheets>
     <sheet name="CNCPIYOY" sheetId="1" r:id="rId1"/>
@@ -77,15 +77,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -93,13 +93,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -107,7 +107,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -158,40 +158,40 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="백분율" xfId="2" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -209,7 +209,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4287,17 +4287,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A2DF88-805C-2E4E-A3EC-9F545567B7EC}">
   <dimension ref="A1:I489"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.36328125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="10.81640625" style="5"/>
+    <col min="1" max="1" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.33203125" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>31413</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="H2" s="11"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>31444</v>
       </c>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="H3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>31472</v>
       </c>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>31503</v>
       </c>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>31533</v>
       </c>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>31564</v>
       </c>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>31594</v>
       </c>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>31625</v>
       </c>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>31656</v>
       </c>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>31686</v>
       </c>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>31717</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>31747</v>
       </c>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>31778</v>
       </c>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>31809</v>
       </c>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>31837</v>
       </c>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>31868</v>
       </c>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>31898</v>
       </c>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>31929</v>
       </c>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>31959</v>
       </c>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>31990</v>
       </c>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="H21" s="11"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>32021</v>
       </c>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H22" s="11"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>32051</v>
       </c>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H23" s="11"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>32082</v>
       </c>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H24" s="11"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>32112</v>
       </c>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="H25" s="11"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>32143</v>
       </c>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="H26" s="11"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>32174</v>
       </c>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="H27" s="11"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>32203</v>
       </c>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H28" s="11"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>32234</v>
       </c>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>32264</v>
       </c>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>32295</v>
       </c>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H31" s="11"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>32325</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>32356</v>
       </c>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>32387</v>
       </c>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>32417</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>32448</v>
       </c>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>32478</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>32509</v>
       </c>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>32540</v>
       </c>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>32568</v>
       </c>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>32599</v>
       </c>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>32629</v>
       </c>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>32660</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>32690</v>
       </c>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>32721</v>
       </c>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>32752</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>32782</v>
       </c>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H47" s="11"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>32813</v>
       </c>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H48" s="11"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>32843</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H49" s="11"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>32874</v>
       </c>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H50" s="11"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>32905</v>
       </c>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>32933</v>
       </c>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="H52" s="11"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>32964</v>
       </c>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>32994</v>
       </c>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="H54" s="11"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>33025</v>
       </c>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="H55" s="11"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>33055</v>
       </c>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="H56" s="11"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>33086</v>
       </c>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H57" s="11"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>33117</v>
       </c>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H58" s="11"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>33147</v>
       </c>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="H59" s="11"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>33178</v>
       </c>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H60" s="11"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>33208</v>
       </c>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="H61" s="11"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>33239</v>
       </c>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="H62" s="11"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>33270</v>
       </c>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H63" s="11"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>33298</v>
       </c>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="H64" s="11"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>33329</v>
       </c>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="H65" s="11"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>33359</v>
       </c>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="H66" s="11"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>33390</v>
       </c>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="H67" s="11"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>33420</v>
       </c>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="H68" s="11"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>33451</v>
       </c>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="H69" s="11"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>33482</v>
       </c>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H70" s="11"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>33512</v>
       </c>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H71" s="11"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>33543</v>
       </c>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="H72" s="11"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>33573</v>
       </c>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="H73" s="11"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>33604</v>
       </c>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="H74" s="11"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>33635</v>
       </c>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H75" s="11"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>33664</v>
       </c>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H76" s="11"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>33695</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="H77" s="11"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>33725</v>
       </c>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="H78" s="11"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>33756</v>
       </c>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="H79" s="11"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>33786</v>
       </c>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>33817</v>
       </c>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>33848</v>
       </c>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>33878</v>
       </c>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>33909</v>
       </c>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>33939</v>
       </c>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="H85" s="11"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>33970</v>
       </c>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="H86" s="11"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>34001</v>
       </c>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>34029</v>
       </c>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>34060</v>
       </c>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>34090</v>
       </c>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="H90" s="11"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>34121</v>
       </c>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="H91" s="11"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="7">
         <v>34151</v>
       </c>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H92" s="11"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>34182</v>
       </c>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="H93" s="11"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>34213</v>
       </c>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="H94" s="11"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <v>34243</v>
       </c>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="H95" s="11"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <v>34274</v>
       </c>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="H96" s="11"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>34304</v>
       </c>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="H97" s="11"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>34335</v>
       </c>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="H98" s="11"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <v>34366</v>
       </c>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="H99" s="11"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>34394</v>
       </c>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="H100" s="11"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>34425</v>
       </c>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="H101" s="11"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <v>34455</v>
       </c>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="H102" s="11"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>34486</v>
       </c>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H103" s="11"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>34516</v>
       </c>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="H104" s="11"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <v>34547</v>
       </c>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="H105" s="11"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <v>34578</v>
       </c>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="H106" s="11"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>34608</v>
       </c>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H107" s="11"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <v>34639</v>
       </c>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="H108" s="11"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>34669</v>
       </c>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="H109" s="11"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>34700</v>
       </c>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H110" s="11"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <v>34731</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H111" s="11"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>34759</v>
       </c>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="H112" s="11"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>34790</v>
       </c>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="H113" s="11"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
         <v>34820</v>
       </c>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="H114" s="11"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
         <v>34851</v>
       </c>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H115" s="11"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
         <v>34881</v>
       </c>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="H116" s="11"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>34912</v>
       </c>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="H117" s="11"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
         <v>34943</v>
       </c>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="H118" s="11"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>34973</v>
       </c>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="H119" s="11"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <v>35004</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="H120" s="11"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>35034</v>
       </c>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H121" s="11"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>35065</v>
       </c>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="H122" s="11"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <v>35096</v>
       </c>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="H123" s="11"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <v>35125</v>
       </c>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="H124" s="11"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <v>35156</v>
       </c>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="H125" s="11"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>35186</v>
       </c>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H126" s="11"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <v>35217</v>
       </c>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="H127" s="11"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>35247</v>
       </c>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H128" s="11"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>35278</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="H129" s="11"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <v>35309</v>
       </c>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="H130" s="11"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>35339</v>
       </c>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H131" s="11"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>35370</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H132" s="11"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <v>35400</v>
       </c>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="H133" s="11"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <v>35431</v>
       </c>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="H134" s="11"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <v>35462</v>
       </c>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="H135" s="11"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>35490</v>
       </c>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="H136" s="11"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>35521</v>
       </c>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="H137" s="11"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>35551</v>
       </c>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="H138" s="11"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>35582</v>
       </c>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="H139" s="11"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>35612</v>
       </c>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="H140" s="11"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>35643</v>
       </c>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="H141" s="11"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>35674</v>
       </c>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="H142" s="11"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>35704</v>
       </c>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="H143" s="11"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>35735</v>
       </c>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="H144" s="11"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>35765</v>
       </c>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="H145" s="11"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>35796</v>
       </c>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="H146" s="11"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>35827</v>
       </c>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H147" s="11"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>35855</v>
       </c>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H148" s="11"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>35886</v>
       </c>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H149" s="11"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>35916</v>
       </c>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="H150" s="11"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>35947</v>
       </c>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="H151" s="11"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>35977</v>
       </c>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="H152" s="11"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>36008</v>
       </c>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="H153" s="11"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>36039</v>
       </c>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H154" s="11"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>36069</v>
       </c>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H155" s="11"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>36100</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="H156" s="11"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>36130</v>
       </c>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H157" s="11"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <v>36161</v>
       </c>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H158" s="11"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="7">
         <v>36192</v>
       </c>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="H159" s="11"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="7">
         <v>36220</v>
       </c>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="H160" s="11"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="7">
         <v>36251</v>
       </c>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="H161" s="11"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="7">
         <v>36281</v>
       </c>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H162" s="11"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="7">
         <v>36312</v>
       </c>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="H163" s="11"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="7">
         <v>36342</v>
       </c>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="H164" s="11"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="7">
         <v>36373</v>
       </c>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="H165" s="11"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <v>36404</v>
       </c>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H166" s="11"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <v>36434</v>
       </c>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="H167" s="11"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <v>36465</v>
       </c>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="H168" s="11"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <v>36495</v>
       </c>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="H169" s="11"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <v>36526</v>
       </c>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="H170" s="11"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <v>36557</v>
       </c>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="H171" s="11"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <v>36586</v>
       </c>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H172" s="11"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <v>36617</v>
       </c>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="H173" s="11"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <v>36647</v>
       </c>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="H174" s="11"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <v>36678</v>
       </c>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="H175" s="11"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <v>36708</v>
       </c>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H176" s="11"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <v>36739</v>
       </c>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H177" s="11"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <v>36770</v>
       </c>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="H178" s="11"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <v>36800</v>
       </c>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="H179" s="11"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <v>36831</v>
       </c>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="H180" s="11"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <v>36861</v>
       </c>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="H181" s="11"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <v>36892</v>
       </c>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H182" s="11"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <v>36923</v>
       </c>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="H183" s="11"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>36951</v>
       </c>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H184" s="11"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>36982</v>
       </c>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H185" s="11"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>37012</v>
       </c>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="H186" s="11"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="7">
         <v>37043</v>
       </c>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H187" s="11"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="7">
         <v>37073</v>
       </c>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="H188" s="11"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="7">
         <v>37104</v>
       </c>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H189" s="11"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="7">
         <v>37135</v>
       </c>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="H190" s="11"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="7">
         <v>37165</v>
       </c>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H191" s="11"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="7">
         <v>37196</v>
       </c>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H192" s="11"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="7">
         <v>37226</v>
       </c>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H193" s="11"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="7">
         <v>37257</v>
       </c>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="H194" s="11"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="7">
         <v>37288</v>
       </c>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="H195" s="11"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="7">
         <v>37316</v>
       </c>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="H196" s="11"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="7">
         <v>37347</v>
       </c>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="H197" s="11"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="7">
         <v>37377</v>
       </c>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H198" s="11"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="7">
         <v>37408</v>
       </c>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="H199" s="11"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="7">
         <v>37438</v>
       </c>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="H200" s="11"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="7">
         <v>37469</v>
       </c>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="H201" s="11"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="7">
         <v>37500</v>
       </c>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="H202" s="11"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="7">
         <v>37530</v>
       </c>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="H203" s="11"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <v>37561</v>
       </c>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H204" s="11"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <v>37591</v>
       </c>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="H205" s="11"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <v>37622</v>
       </c>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="H206" s="11"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <v>37653</v>
       </c>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="H207" s="11"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <v>37681</v>
       </c>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="H208" s="11"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="7">
         <v>37712</v>
       </c>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="H209" s="11"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="7">
         <v>37742</v>
       </c>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="H210" s="11"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="7">
         <v>37773</v>
       </c>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="H211" s="11"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="7">
         <v>37803</v>
       </c>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="H212" s="11"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="7">
         <v>37834</v>
       </c>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H213" s="11"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="7">
         <v>37865</v>
       </c>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="H214" s="11"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="7">
         <v>37895</v>
       </c>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="H215" s="11"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="7">
         <v>37926</v>
       </c>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="H216" s="11"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="7">
         <v>37956</v>
       </c>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="H217" s="11"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="7">
         <v>37987</v>
       </c>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="H218" s="11"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="7">
         <v>38018</v>
       </c>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="H219" s="11"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="7">
         <v>38047</v>
       </c>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="H220" s="11"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="7">
         <v>38078</v>
       </c>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="H221" s="11"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="7">
         <v>38108</v>
       </c>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="H222" s="11"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="7">
         <v>38139</v>
       </c>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H223" s="11"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="7">
         <v>38169</v>
       </c>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="H224" s="11"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="7">
         <v>38200</v>
       </c>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="H225" s="11"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="7">
         <v>38231</v>
       </c>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="H226" s="11"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>38261</v>
       </c>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="H227" s="11"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>38292</v>
       </c>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="H228" s="11"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="7">
         <v>38322</v>
       </c>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H229" s="11"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="7">
         <v>38353</v>
       </c>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="H230" s="11"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="7">
         <v>38384</v>
       </c>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="H231" s="11"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="7">
         <v>38412</v>
       </c>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="H232" s="11"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="7">
         <v>38443</v>
       </c>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H233" s="11"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>38473</v>
       </c>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="H234" s="11"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>38504</v>
       </c>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H235" s="11"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="7">
         <v>38534</v>
       </c>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="H236" s="11"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="7">
         <v>38565</v>
       </c>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="H237" s="11"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="7">
         <v>38596</v>
       </c>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="H238" s="11"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="7">
         <v>38626</v>
       </c>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="H239" s="11"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="7">
         <v>38657</v>
       </c>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="H240" s="11"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="7">
         <v>38687</v>
       </c>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="H241" s="11"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="7">
         <v>38718</v>
       </c>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="H242" s="11"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="7">
         <v>38749</v>
       </c>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H243" s="11"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="7">
         <v>38777</v>
       </c>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="H244" s="11"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="7">
         <v>38808</v>
       </c>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="H245" s="11"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="7">
         <v>38838</v>
       </c>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="H246" s="11"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="7">
         <v>38869</v>
       </c>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H247" s="11"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="7">
         <v>38899</v>
       </c>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H248" s="11"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="7">
         <v>38930</v>
       </c>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="H249" s="11"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="7">
         <v>38961</v>
       </c>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="H250" s="11"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="7">
         <v>38991</v>
       </c>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="H251" s="11"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="7">
         <v>39022</v>
       </c>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="H252" s="11"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="7">
         <v>39052</v>
       </c>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H253" s="11"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7">
         <v>39083</v>
       </c>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="H254" s="11"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="7">
         <v>39114</v>
       </c>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="H255" s="11"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="7">
         <v>39142</v>
       </c>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="H256" s="11"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="7">
         <v>39173</v>
       </c>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="H257" s="11"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="7">
         <v>39203</v>
       </c>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="H258" s="11"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="7">
         <v>39234</v>
       </c>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="H259" s="11"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="7">
         <v>39264</v>
       </c>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="H260" s="11"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="7">
         <v>39295</v>
       </c>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="H261" s="11"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="7">
         <v>39326</v>
       </c>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="H262" s="11"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="7">
         <v>39356</v>
       </c>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="H263" s="11"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="7">
         <v>39387</v>
       </c>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="H264" s="11"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="7">
         <v>39417</v>
       </c>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="H265" s="11"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="7">
         <v>39448</v>
       </c>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="H266" s="11"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="7">
         <v>39479</v>
       </c>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="H267" s="11"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="7">
         <v>39508</v>
       </c>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H268" s="11"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="7">
         <v>39539</v>
       </c>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="H269" s="11"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="7">
         <v>39569</v>
       </c>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H270" s="11"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="7">
         <v>39600</v>
       </c>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H271" s="11"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="7">
         <v>39630</v>
       </c>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="H272" s="11"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="7">
         <v>39661</v>
       </c>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="H273" s="11"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="7">
         <v>39692</v>
       </c>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="H274" s="11"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="7">
         <v>39722</v>
       </c>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H275" s="11"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="7">
         <v>39753</v>
       </c>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="H276" s="11"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="7">
         <v>39783</v>
       </c>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="H277" s="11"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="7">
         <v>39814</v>
       </c>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="H278" s="11"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="7">
         <v>39845</v>
       </c>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="H279" s="11"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="7">
         <v>39873</v>
       </c>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H280" s="11"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="7">
         <v>39904</v>
       </c>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="H281" s="11"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="7">
         <v>39934</v>
       </c>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="H282" s="11"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="7">
         <v>39965</v>
       </c>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H283" s="11"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="7">
         <v>39995</v>
       </c>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H284" s="11"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="7">
         <v>40026</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="H285" s="11"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="7">
         <v>40057</v>
       </c>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="H286" s="11"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="7">
         <v>40087</v>
       </c>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="H287" s="11"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="7">
         <v>40118</v>
       </c>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="H288" s="11"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="7">
         <v>40148</v>
       </c>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="H289" s="11"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="7">
         <v>40179</v>
       </c>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="H290" s="11"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="7">
         <v>40210</v>
       </c>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="H291" s="11"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="7">
         <v>40238</v>
       </c>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H292" s="11"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="7">
         <v>40269</v>
       </c>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="H293" s="11"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="7">
         <v>40299</v>
       </c>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H294" s="11"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="7">
         <v>40330</v>
       </c>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="H295" s="11"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="7">
         <v>40360</v>
       </c>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="H296" s="11"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="7">
         <v>40391</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H297" s="11"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="7">
         <v>40422</v>
       </c>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="H298" s="11"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="7">
         <v>40452</v>
       </c>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="H299" s="11"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="7">
         <v>40483</v>
       </c>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="H300" s="11"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="7">
         <v>40513</v>
       </c>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="H301" s="11"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="7">
         <v>40544</v>
       </c>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="H302" s="11"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="7">
         <v>40575</v>
       </c>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="H303" s="11"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="7">
         <v>40603</v>
       </c>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H304" s="11"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="7">
         <v>40634</v>
       </c>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="H305" s="11"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="7">
         <v>40664</v>
       </c>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="H306" s="11"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="7">
         <v>40695</v>
       </c>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="H307" s="11"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="7">
         <v>40725</v>
       </c>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="H308" s="11"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="7">
         <v>40756</v>
       </c>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="H309" s="11"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="7">
         <v>40787</v>
       </c>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="H310" s="11"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="7">
         <v>40817</v>
       </c>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="H311" s="11"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="7">
         <v>40848</v>
       </c>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="H312" s="11"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="7">
         <v>40878</v>
       </c>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="H313" s="11"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="7">
         <v>40909</v>
       </c>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H314" s="11"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="7">
         <v>40940</v>
       </c>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="H315" s="11"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="7">
         <v>40969</v>
       </c>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="H316" s="11"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="7">
         <v>41000</v>
       </c>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="H317" s="11"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="7">
         <v>41030</v>
       </c>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H318" s="11"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="7">
         <v>41061</v>
       </c>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="H319" s="11"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="7">
         <v>41091</v>
       </c>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="H320" s="11"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="7">
         <v>41122</v>
       </c>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="H321" s="11"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="7">
         <v>41153</v>
       </c>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="H322" s="11"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="7">
         <v>41183</v>
       </c>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="H323" s="11"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="7">
         <v>41214</v>
       </c>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="H324" s="11"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="7">
         <v>41244</v>
       </c>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="H325" s="11"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="7">
         <v>41275</v>
       </c>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="H326" s="11"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="7">
         <v>41306</v>
       </c>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="H327" s="11"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="7">
         <v>41334</v>
       </c>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="H328" s="11"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="7">
         <v>41365</v>
       </c>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="H329" s="11"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="7">
         <v>41395</v>
       </c>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="H330" s="11"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="7">
         <v>41426</v>
       </c>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="H331" s="11"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="7">
         <v>41456</v>
       </c>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="H332" s="11"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="7">
         <v>41487</v>
       </c>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="H333" s="11"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="7">
         <v>41518</v>
       </c>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="H334" s="11"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="7">
         <v>41548</v>
       </c>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="H335" s="11"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="7">
         <v>41579</v>
       </c>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="H336" s="11"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="7">
         <v>41609</v>
       </c>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="H337" s="11"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="7">
         <v>41640</v>
       </c>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="H338" s="11"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="7">
         <v>41671</v>
       </c>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="H339" s="11"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="7">
         <v>41699</v>
       </c>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="H340" s="11"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="7">
         <v>41730</v>
       </c>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="H341" s="11"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="7">
         <v>41760</v>
       </c>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="H342" s="11"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="7">
         <v>41791</v>
       </c>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="H343" s="11"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="7">
         <v>41821</v>
       </c>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="H344" s="11"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="7">
         <v>41852</v>
       </c>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H345" s="11"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="7">
         <v>41883</v>
       </c>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="H346" s="11"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="7">
         <v>41913</v>
       </c>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="H347" s="11"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="7">
         <v>41944</v>
       </c>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="H348" s="11"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="7">
         <v>41974</v>
       </c>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="H349" s="11"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="7">
         <v>42005</v>
       </c>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="H350" s="11"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="7">
         <v>42036</v>
       </c>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="H351" s="11"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="7">
         <v>42064</v>
       </c>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="H352" s="11"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="7">
         <v>42095</v>
       </c>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="H353" s="11"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="7">
         <v>42125</v>
       </c>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="H354" s="11"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="7">
         <v>42156</v>
       </c>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="H355" s="11"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="7">
         <v>42186</v>
       </c>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="H356" s="11"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="7">
         <v>42217</v>
       </c>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="H357" s="11"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="7">
         <v>42248</v>
       </c>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="H358" s="11"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="7">
         <v>42278</v>
       </c>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="H359" s="11"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="7">
         <v>42309</v>
       </c>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="H360" s="11"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="7">
         <v>42339</v>
       </c>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="H361" s="11"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="7">
         <v>42370</v>
       </c>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="H362" s="11"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="7">
         <v>42401</v>
       </c>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="H363" s="11"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="7">
         <v>42430</v>
       </c>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="H364" s="11"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="7">
         <v>42461</v>
       </c>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H365" s="11"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="7">
         <v>42491</v>
       </c>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="H366" s="11"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="7">
         <v>42522</v>
       </c>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="H367" s="11"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="7">
         <v>42552</v>
       </c>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="H368" s="11"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="7">
         <v>42583</v>
       </c>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="H369" s="11"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="7">
         <v>42614</v>
       </c>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="H370" s="11"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="7">
         <v>42644</v>
       </c>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="H371" s="11"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="7">
         <v>42675</v>
       </c>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="H372" s="11"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="7">
         <v>42705</v>
       </c>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="H373" s="11"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="7">
         <v>42736</v>
       </c>
@@ -13274,7 +13274,7 @@
       </c>
       <c r="H374" s="11"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="7">
         <v>42767</v>
       </c>
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H375" s="11"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="7">
         <v>42795</v>
       </c>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H376" s="11"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="7">
         <v>42826</v>
       </c>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="H377" s="11"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="7">
         <v>42856</v>
       </c>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="H378" s="11"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="7">
         <v>42887</v>
       </c>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="H379" s="11"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="7">
         <v>42917</v>
       </c>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="H380" s="11"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="7">
         <v>42948</v>
       </c>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="H381" s="11"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="7">
         <v>42979</v>
       </c>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="H382" s="11"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="7">
         <v>43009</v>
       </c>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="H383" s="11"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="7">
         <v>43040</v>
       </c>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="H384" s="11"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="7">
         <v>43070</v>
       </c>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="H385" s="11"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="7">
         <v>43101</v>
       </c>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="H386" s="11"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="7">
         <v>43132</v>
       </c>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="H387" s="11"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="7">
         <v>43160</v>
       </c>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="H388" s="11"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="7">
         <v>43191</v>
       </c>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="H389" s="11"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="7">
         <v>43221</v>
       </c>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="H390" s="11"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="7">
         <v>43252</v>
       </c>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="H391" s="11"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="7">
         <v>43282</v>
       </c>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="H392" s="11"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="7">
         <v>43313</v>
       </c>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="H393" s="11"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="7">
         <v>43344</v>
       </c>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="H394" s="11"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="7">
         <v>43374</v>
       </c>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="H395" s="11"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="7">
         <v>43405</v>
       </c>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="H396" s="11"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="7">
         <v>43435</v>
       </c>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="H397" s="11"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="7">
         <v>43466</v>
       </c>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="H398" s="11"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="7">
         <v>43497</v>
       </c>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="H399" s="11"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="7">
         <v>43525</v>
       </c>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="H400" s="11"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="7">
         <v>43556</v>
       </c>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="H401" s="11"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="7">
         <v>43586</v>
       </c>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="H402" s="11"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="7">
         <v>43617</v>
       </c>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="H403" s="11"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="7">
         <v>43647</v>
       </c>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H404" s="11"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="7">
         <v>43678</v>
       </c>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="H405" s="11"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="7">
         <v>43709</v>
       </c>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H406" s="11"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="7">
         <v>43739</v>
       </c>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="H407" s="11"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="7">
         <v>43770</v>
       </c>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="H408" s="11"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="7">
         <v>43800</v>
       </c>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="H409" s="11"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="7">
         <v>43831</v>
       </c>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="H410" s="11"/>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="7">
         <v>43862</v>
       </c>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="H411" s="11"/>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="7">
         <v>43891</v>
       </c>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="H412" s="11"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" s="7">
         <v>43922</v>
       </c>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="H413" s="11"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="7">
         <v>43952</v>
       </c>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="H414" s="11"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="7">
         <v>43983</v>
       </c>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="H415" s="11"/>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="7">
         <v>44013</v>
       </c>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H416" s="11"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="7">
         <v>44044</v>
       </c>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="H417" s="11"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="7">
         <v>44075</v>
       </c>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="H418" s="11"/>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="7">
         <v>44105</v>
       </c>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="H419" s="11"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="7">
         <v>44136</v>
       </c>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="H420" s="11"/>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="7">
         <v>44166</v>
       </c>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="H421" s="11"/>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="7">
         <v>44197</v>
       </c>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="H422" s="11"/>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="7">
         <v>44228</v>
       </c>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H423" s="11"/>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="7">
         <v>44256</v>
       </c>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="H424" s="11"/>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="7">
         <v>44287</v>
       </c>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="H425" s="11"/>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="7">
         <v>44317</v>
       </c>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H426" s="11"/>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="7">
         <v>44348</v>
       </c>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="H427" s="11"/>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="7">
         <v>44378</v>
       </c>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="H428" s="11"/>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="7">
         <v>44409</v>
       </c>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="H429" s="11"/>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="7">
         <v>44440</v>
       </c>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="H430" s="11"/>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="7">
         <v>44470</v>
       </c>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="H431" s="11"/>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="7">
         <v>44501</v>
       </c>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="H432" s="11"/>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" s="7">
         <v>44531</v>
       </c>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="H433" s="11"/>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" s="7">
         <v>44562</v>
       </c>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="H434" s="11"/>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" s="7">
         <v>44593</v>
       </c>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="H435" s="11"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" s="7">
         <v>44621</v>
       </c>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H436" s="11"/>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="7">
         <v>44652</v>
       </c>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="H437" s="11"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="7">
         <v>44682</v>
       </c>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="H438" s="11"/>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="7">
         <v>44713</v>
       </c>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="H439" s="11"/>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="7">
         <v>44743</v>
       </c>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="H440" s="11"/>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="7">
         <v>44774</v>
       </c>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="H441" s="11"/>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="7">
         <v>44805</v>
       </c>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="H442" s="11"/>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" s="7">
         <v>44835</v>
       </c>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="H443" s="11"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="7">
         <v>44866</v>
       </c>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="H444" s="11"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="7">
         <v>44896</v>
       </c>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="H445" s="11"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" s="7">
         <v>44927</v>
       </c>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="H446" s="11"/>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="7">
         <v>44958</v>
       </c>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="H447" s="11"/>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="7">
         <v>44986</v>
       </c>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="H448" s="11"/>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" s="7">
         <v>45017</v>
       </c>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="H449" s="11"/>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" s="7">
         <v>45047</v>
       </c>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="H450" s="11"/>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" s="7">
         <v>45078</v>
       </c>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="H451" s="11"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="7">
         <v>45108</v>
       </c>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="H452" s="11"/>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="7">
         <v>45139</v>
       </c>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="H453" s="11"/>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="7">
         <v>45170</v>
       </c>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="H454" s="11"/>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="7">
         <v>45200</v>
       </c>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="H455" s="11"/>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="7">
         <v>45231</v>
       </c>
@@ -15242,7 +15242,7 @@
       </c>
       <c r="H456" s="11"/>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="7">
         <v>45261</v>
       </c>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="H457" s="11"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="7">
         <v>45292</v>
       </c>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="H458" s="11"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="7">
         <v>45323</v>
       </c>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="H459" s="11"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="7">
         <v>45352</v>
       </c>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="H460" s="11"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="7">
         <v>45383</v>
       </c>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H461" s="11"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="7">
         <v>45413</v>
       </c>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="H462" s="11"/>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="7">
         <v>45444</v>
       </c>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="H463" s="11"/>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="7">
         <v>45474</v>
       </c>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="H464" s="11"/>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="7">
         <v>45505</v>
       </c>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="H465" s="11"/>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="7">
         <v>45536</v>
       </c>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="H466" s="11"/>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="7">
         <v>45566</v>
       </c>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="H467" s="11"/>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="7">
         <v>45597</v>
       </c>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="H468" s="11"/>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="7">
         <v>45627</v>
       </c>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="H469" s="11"/>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="7">
         <v>45658</v>
       </c>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="H470" s="11"/>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="7">
         <v>45689</v>
       </c>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="H471" s="11"/>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="7">
         <v>45717</v>
       </c>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="H472" s="11"/>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="7">
         <v>45748</v>
       </c>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="H473" s="11"/>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="7">
         <v>45778</v>
       </c>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="H474" s="11"/>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="7">
         <v>45809</v>
       </c>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="H475" s="11"/>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="7">
         <v>45839</v>
       </c>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="H476" s="11"/>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="7">
         <v>45870</v>
       </c>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="H477" s="11"/>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="7">
         <v>45901</v>
       </c>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="H478" s="11"/>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="7">
         <v>45931</v>
       </c>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="H479" s="11"/>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="7">
         <v>45962</v>
       </c>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="H480" s="11"/>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="7">
         <v>45992</v>
       </c>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="H481" s="11"/>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="7">
         <v>46023</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="7">
         <v>46054</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" s="7">
         <v>46082</v>
       </c>
@@ -15911,7 +15911,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" s="7">
         <v>46113</v>
       </c>
@@ -15934,7 +15934,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" s="7">
         <v>46143</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="7">
         <v>46174</v>
       </c>
@@ -15980,7 +15980,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" s="7">
         <v>46204</v>
       </c>
@@ -16003,7 +16003,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="7">
         <v>46235</v>
       </c>
@@ -16033,7 +16033,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91024DA1-00F0-4602-9985-01AD43B6ED3C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16044,12 +16044,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651FE52F-B836-C048-8E04-77D870B1C558}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.36328125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="8.36328125" style="5"/>
+    <col min="1" max="16384" width="8.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
